--- a/ParallelLSTM/result/data/예측결과/testdata증강/관심강우mae/240723_mae.xlsx
+++ b/ParallelLSTM/result/data/예측결과/testdata증강/관심강우mae/240723_mae.xlsx
@@ -548,7 +548,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-07-23 12:40</t>
+          <t>2024-07-23 12:30:00</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -590,34 +590,34 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>-0.0236530563163504</v>
+        <v>0.5535707608221714</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.09539016845954855</v>
+        <v>0.03611705551040129</v>
       </c>
       <c r="R2" t="n">
-        <v>0.227118204302258</v>
+        <v>0.102329421573215</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3088529884258019</v>
+        <v>0.1900448776221061</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.573503694060822</v>
+        <v>0.01438935228743421</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1908678359258556</v>
+        <v>0.04686236403953908</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3305488453971016</v>
+        <v>0.1858455239401924</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4368842362981933</v>
+        <v>0.2164771674785567</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-07-23 12:50</t>
+          <t>2024-07-23 12:40:00</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -639,16 +639,16 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="I3" t="n">
-        <v>17.35</v>
+        <v>17.85</v>
       </c>
       <c r="J3" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="K3" t="n">
-        <v>57.54</v>
+        <v>58.47</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -670,7 +670,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-07-23 13:00</t>
+          <t>2024-07-23 12:50:00</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -698,10 +698,10 @@
         <v>17.35</v>
       </c>
       <c r="J4" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="K4" t="n">
-        <v>56.61</v>
+        <v>57.54</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -723,7 +723,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-07-23 13:10</t>
+          <t>2024-07-23 13:00:00</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -733,7 +733,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -757,7 +757,7 @@
         <v>56.61</v>
       </c>
       <c r="L5" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -776,7 +776,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-07-23 13:20</t>
+          <t>2024-07-23 13:10:00</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -798,19 +798,19 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="I6" t="n">
-        <v>16.86</v>
+        <v>17.35</v>
       </c>
       <c r="J6" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="K6" t="n">
-        <v>55.68</v>
+        <v>56.61</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -829,7 +829,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-07-23 13:30</t>
+          <t>2024-07-23 13:20:00</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -857,10 +857,10 @@
         <v>16.86</v>
       </c>
       <c r="J7" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="K7" t="n">
-        <v>54.76</v>
+        <v>55.68</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -882,7 +882,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-07-23 13:40</t>
+          <t>2024-07-23 13:30:00</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -935,7 +935,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-07-23 13:50</t>
+          <t>2024-07-23 13:40:00</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -963,10 +963,10 @@
         <v>16.86</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="K9" t="n">
-        <v>53.85</v>
+        <v>54.76</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-07-23 14:00</t>
+          <t>2024-07-23 13:50:00</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1016,10 +1016,10 @@
         <v>16.86</v>
       </c>
       <c r="J10" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="K10" t="n">
-        <v>52.95</v>
+        <v>53.85</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1041,7 +1041,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-07-23 14:10</t>
+          <t>2024-07-23 14:00:00</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1063,10 +1063,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="I11" t="n">
-        <v>16.38</v>
+        <v>16.86</v>
       </c>
       <c r="J11" t="n">
         <v>2.49</v>
@@ -1094,7 +1094,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-07-23 14:20</t>
+          <t>2024-07-23 14:10:00</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1122,10 +1122,10 @@
         <v>16.38</v>
       </c>
       <c r="J12" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="K12" t="n">
-        <v>52.05</v>
+        <v>52.95</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-07-23 14:30</t>
+          <t>2024-07-23 14:20:00</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1200,7 +1200,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-07-23 14:40</t>
+          <t>2024-07-23 14:30:00</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1228,10 +1228,10 @@
         <v>16.38</v>
       </c>
       <c r="J14" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="K14" t="n">
-        <v>51.16</v>
+        <v>52.05</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1253,7 +1253,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-07-23 14:50</t>
+          <t>2024-07-23 14:40:00</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1306,7 +1306,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-07-23 15:00</t>
+          <t>2024-07-23 14:50:00</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1328,16 +1328,16 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I16" t="n">
-        <v>15.9</v>
+        <v>16.38</v>
       </c>
       <c r="J16" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="K16" t="n">
-        <v>50.27</v>
+        <v>51.16</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1359,7 +1359,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024-07-23 15:10</t>
+          <t>2024-07-23 15:00:00</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1387,10 +1387,10 @@
         <v>15.9</v>
       </c>
       <c r="J17" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="K17" t="n">
-        <v>49.39</v>
+        <v>50.27</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024-07-23 15:20</t>
+          <t>2024-07-23 15:10:00</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>1.12</v>
@@ -1446,10 +1446,10 @@
         <v>49.39</v>
       </c>
       <c r="L18" t="n">
-        <v>0.251</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1465,7 +1465,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024-07-23 15:30</t>
+          <t>2024-07-23 15:20:00</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1484,7 +1484,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>1.12</v>
@@ -1493,16 +1493,16 @@
         <v>15.9</v>
       </c>
       <c r="J19" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="K19" t="n">
-        <v>48.52</v>
+        <v>49.39</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.251</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1518,7 +1518,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024-07-23 15:40</t>
+          <t>2024-07-23 15:30:00</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1571,7 +1571,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024-07-23 15:50</t>
+          <t>2024-07-23 15:40:00</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1599,10 +1599,10 @@
         <v>15.9</v>
       </c>
       <c r="J21" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="K21" t="n">
-        <v>47.65</v>
+        <v>48.52</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024-07-23 16:00</t>
+          <t>2024-07-23 15:50:00</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1677,7 +1677,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024-07-23 16:10</t>
+          <t>2024-07-23 16:00:00</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1699,10 +1699,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>15.43</v>
+        <v>15.9</v>
       </c>
       <c r="J23" t="n">
         <v>2.43</v>
@@ -1730,7 +1730,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024-07-23 16:20</t>
+          <t>2024-07-23 16:10:00</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1758,10 +1758,10 @@
         <v>15.43</v>
       </c>
       <c r="J24" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="K24" t="n">
-        <v>46.79</v>
+        <v>47.65</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024-07-23 16:30</t>
+          <t>2024-07-23 16:20:00</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1836,7 +1836,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2024-07-23 16:40</t>
+          <t>2024-07-23 16:30:00</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1864,10 +1864,10 @@
         <v>15.43</v>
       </c>
       <c r="J26" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="K26" t="n">
-        <v>45.93</v>
+        <v>46.79</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1889,7 +1889,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024-07-23 16:50</t>
+          <t>2024-07-23 16:40:00</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1942,7 +1942,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024-07-23 17:00</t>
+          <t>2024-07-23 16:50:00</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I28" t="n">
-        <v>14.97</v>
+        <v>15.43</v>
       </c>
       <c r="J28" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="K28" t="n">
-        <v>45.08</v>
+        <v>45.93</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024-07-23 17:10</t>
+          <t>2024-07-23 17:00:00</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2048,7 +2048,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024-07-23 17:20</t>
+          <t>2024-07-23 17:10:00</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2101,7 +2101,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2024-07-23 17:30</t>
+          <t>2024-07-23 17:20:00</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2129,10 +2129,10 @@
         <v>14.97</v>
       </c>
       <c r="J31" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="K31" t="n">
-        <v>44.24</v>
+        <v>45.08</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024-07-23 17:40</t>
+          <t>2024-07-23 17:30:00</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2207,7 +2207,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2024-07-23 17:50</t>
+          <t>2024-07-23 17:40:00</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2235,10 +2235,10 @@
         <v>14.97</v>
       </c>
       <c r="J33" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="K33" t="n">
-        <v>43.41</v>
+        <v>44.24</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2260,7 +2260,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024-07-23 18:00</t>
+          <t>2024-07-23 17:50:00</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2313,7 +2313,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024-07-23 18:10</t>
+          <t>2024-07-23 18:00:00</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2335,10 +2335,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I35" t="n">
-        <v>14.51</v>
+        <v>14.97</v>
       </c>
       <c r="J35" t="n">
         <v>2.38</v>
@@ -2366,7 +2366,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2024-07-23 18:20</t>
+          <t>2024-07-23 18:10:00</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2394,10 +2394,10 @@
         <v>14.51</v>
       </c>
       <c r="J36" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="K36" t="n">
-        <v>42.58</v>
+        <v>43.41</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2024-07-23 18:30</t>
+          <t>2024-07-23 18:20:00</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2472,7 +2472,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2024-07-23 18:40</t>
+          <t>2024-07-23 18:30:00</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -2506,16 +2506,16 @@
         <v>42.58</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.804</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.071066737174988</v>
+        <v>1.089526772499084</v>
       </c>
       <c r="O38" t="n">
-        <v>2.413789987564087</v>
+        <v>2.367097616195679</v>
       </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
@@ -2529,7 +2529,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2024-07-23 18:50</t>
+          <t>2024-07-23 18:40:00</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2542,13 +2542,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>1.09</v>
@@ -2557,22 +2557,22 @@
         <v>14.51</v>
       </c>
       <c r="J39" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="K39" t="n">
-        <v>41.76</v>
+        <v>42.58</v>
       </c>
       <c r="L39" t="n">
-        <v>0.774</v>
+        <v>0.5</v>
       </c>
       <c r="M39" t="n">
-        <v>2.39</v>
+        <v>1.804</v>
       </c>
       <c r="N39" t="n">
-        <v>1.144660234451294</v>
+        <v>1.09356677532196</v>
       </c>
       <c r="O39" t="n">
-        <v>2.383169174194336</v>
+        <v>2.368330240249634</v>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
@@ -2586,7 +2586,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2024-07-23 19:00</t>
+          <t>2024-07-23 18:50:00</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2599,13 +2599,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
         <v>3</v>
       </c>
-      <c r="F40" t="n">
-        <v>14</v>
-      </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
         <v>1.09</v>
@@ -2620,16 +2620,16 @@
         <v>41.76</v>
       </c>
       <c r="L40" t="n">
-        <v>2.725</v>
+        <v>0.774</v>
       </c>
       <c r="M40" t="n">
-        <v>7.961</v>
+        <v>2.39</v>
       </c>
       <c r="N40" t="n">
-        <v>1.16700267791748</v>
+        <v>1.046602368354797</v>
       </c>
       <c r="O40" t="n">
-        <v>2.369503259658813</v>
+        <v>2.37103009223938</v>
       </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
@@ -2643,32 +2643,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2024-07-23 19:10</t>
+          <t>2024-07-23 19:00:00</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="I41" t="n">
-        <v>17.85</v>
+        <v>14.51</v>
       </c>
       <c r="J41" t="n">
         <v>2.36</v>
@@ -2677,16 +2677,16 @@
         <v>41.76</v>
       </c>
       <c r="L41" t="n">
-        <v>1.409</v>
+        <v>2.725</v>
       </c>
       <c r="M41" t="n">
-        <v>3.157</v>
+        <v>7.961</v>
       </c>
       <c r="N41" t="n">
-        <v>1.228375434875488</v>
+        <v>1.117277026176453</v>
       </c>
       <c r="O41" t="n">
-        <v>2.343343734741211</v>
+        <v>2.372349739074707</v>
       </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
@@ -2700,50 +2700,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2024-07-23 19:20</t>
+          <t>2024-07-23 19:10:00</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="I42" t="n">
-        <v>25.95</v>
+        <v>17.85</v>
       </c>
       <c r="J42" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="K42" t="n">
-        <v>40.94</v>
+        <v>41.76</v>
       </c>
       <c r="L42" t="n">
-        <v>0.318</v>
+        <v>1.409</v>
       </c>
       <c r="M42" t="n">
-        <v>0.451</v>
+        <v>3.157</v>
       </c>
       <c r="N42" t="n">
-        <v>1.312554836273193</v>
+        <v>1.137753009796143</v>
       </c>
       <c r="O42" t="n">
-        <v>2.344090461730957</v>
+        <v>2.37885308265686</v>
       </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -2757,32 +2757,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2024-07-23 19:30</t>
+          <t>2024-07-23 19:20:00</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="I43" t="n">
-        <v>50.27</v>
+        <v>25.95</v>
       </c>
       <c r="J43" t="n">
         <v>2.35</v>
@@ -2791,16 +2791,16 @@
         <v>40.94</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>0.318</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>0.451</v>
       </c>
       <c r="N43" t="n">
-        <v>1.424792528152466</v>
+        <v>1.197780251502991</v>
       </c>
       <c r="O43" t="n">
-        <v>2.320437431335449</v>
+        <v>2.373512029647827</v>
       </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
@@ -2814,7 +2814,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2024-07-23 17:40</t>
+          <t>2024-07-23 19:30:00</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2836,16 +2836,16 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.1</v>
+        <v>1.67</v>
       </c>
       <c r="I44" t="n">
-        <v>14.97</v>
+        <v>50.27</v>
       </c>
       <c r="J44" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="K44" t="n">
-        <v>44.24</v>
+        <v>40.94</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -2854,10 +2854,10 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.563047051429749</v>
+        <v>1.264799952507019</v>
       </c>
       <c r="O44" t="n">
-        <v>2.33864688873291</v>
+        <v>2.392430543899536</v>
       </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
@@ -2871,7 +2871,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2024-07-23 17:50</t>
+          <t>2024-07-23 19:40:00</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2893,16 +2893,16 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>14.97</v>
+        <v>81.92</v>
       </c>
       <c r="J45" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="K45" t="n">
-        <v>43.41</v>
+        <v>40.94</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2911,10 +2911,10 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.628653645515442</v>
+        <v>1.40703809261322</v>
       </c>
       <c r="O45" t="n">
-        <v>2.361493110656738</v>
+        <v>2.429236650466919</v>
       </c>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
@@ -2928,7 +2928,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2024-07-23 18:00</t>
+          <t>2024-07-23 19:50:00</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2950,16 +2950,16 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="I46" t="n">
-        <v>14.97</v>
+        <v>93.47</v>
       </c>
       <c r="J46" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="K46" t="n">
-        <v>43.41</v>
+        <v>40.13</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2968,10 +2968,10 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.648751854896545</v>
+        <v>1.496580243110657</v>
       </c>
       <c r="O46" t="n">
-        <v>2.384675979614258</v>
+        <v>2.422694683074951</v>
       </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
@@ -2985,7 +2985,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2024-07-23 18:10</t>
+          <t>2024-07-23 20:00:00</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -3007,16 +3007,16 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.09</v>
+        <v>2.07</v>
       </c>
       <c r="I47" t="n">
-        <v>14.51</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="K47" t="n">
-        <v>43.41</v>
+        <v>40.13</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3025,10 +3025,10 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1.700546383857727</v>
+        <v>1.583763360977173</v>
       </c>
       <c r="O47" t="n">
-        <v>2.397932529449463</v>
+        <v>2.495447397232056</v>
       </c>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
@@ -3042,7 +3042,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2024-07-23 18:20</t>
+          <t>2024-07-23 20:10:00</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -3064,16 +3064,16 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.09</v>
+        <v>1.94</v>
       </c>
       <c r="I48" t="n">
-        <v>14.51</v>
+        <v>75.45</v>
       </c>
       <c r="J48" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="K48" t="n">
-        <v>42.58</v>
+        <v>40.13</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -3082,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.699786901473999</v>
+        <v>1.627918601036072</v>
       </c>
       <c r="O48" t="n">
-        <v>2.456629991531372</v>
+        <v>2.496404886245728</v>
       </c>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
@@ -3099,7 +3099,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2024-07-23 18:30</t>
+          <t>2024-07-23 20:20:00</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -3121,16 +3121,16 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.09</v>
+        <v>1.8</v>
       </c>
       <c r="I49" t="n">
-        <v>14.51</v>
+        <v>61.6</v>
       </c>
       <c r="J49" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="K49" t="n">
-        <v>42.58</v>
+        <v>40.13</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -3139,10 +3139,10 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1.627650022506714</v>
+        <v>1.670370578765869</v>
       </c>
       <c r="O49" t="n">
-        <v>2.478790521621704</v>
+        <v>2.488181829452515</v>
       </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
@@ -3156,7 +3156,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2024-07-23 18:40</t>
+          <t>2024-07-23 20:30:00</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -3172,34 +3172,34 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1.09</v>
+        <v>1.69</v>
       </c>
       <c r="I50" t="n">
-        <v>14.51</v>
+        <v>51.92</v>
       </c>
       <c r="J50" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="K50" t="n">
-        <v>42.58</v>
+        <v>39.33</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.804</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.584334850311279</v>
+        <v>1.601408720016479</v>
       </c>
       <c r="O50" t="n">
-        <v>2.569496393203735</v>
+        <v>2.495009899139404</v>
       </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
@@ -3213,7 +3213,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2024-07-23 18:50</t>
+          <t>2024-07-23 20:40:00</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -3226,37 +3226,37 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.09</v>
+        <v>1.6</v>
       </c>
       <c r="I51" t="n">
-        <v>14.51</v>
+        <v>44.75</v>
       </c>
       <c r="J51" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="K51" t="n">
-        <v>41.76</v>
+        <v>40.13</v>
       </c>
       <c r="L51" t="n">
-        <v>0.774</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.433962345123291</v>
+        <v>1.57901406288147</v>
       </c>
       <c r="O51" t="n">
-        <v>2.721625804901123</v>
+        <v>2.574921131134033</v>
       </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
@@ -3270,7 +3270,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2024-07-23 19:00</t>
+          <t>2024-07-23 20:50:00</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -3283,37 +3283,37 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="I52" t="n">
-        <v>14.51</v>
+        <v>38.93</v>
       </c>
       <c r="J52" t="n">
-        <v>2.36</v>
+        <v>2.84</v>
       </c>
       <c r="K52" t="n">
-        <v>41.76</v>
+        <v>88.23</v>
       </c>
       <c r="L52" t="n">
-        <v>2.725</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>7.961</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.502169609069824</v>
+        <v>1.506835699081421</v>
       </c>
       <c r="O52" t="n">
-        <v>2.704998254776001</v>
+        <v>2.563970327377319</v>
       </c>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
@@ -3327,14 +3327,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2024-07-23 19:10</t>
+          <t>2024-07-23 21:00:00</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -3343,34 +3343,34 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="I53" t="n">
-        <v>17.85</v>
+        <v>34.88</v>
       </c>
       <c r="J53" t="n">
-        <v>2.36</v>
+        <v>2.93</v>
       </c>
       <c r="K53" t="n">
-        <v>41.76</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>1.409</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.157</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1.64102828502655</v>
+        <v>1.411178350448608</v>
       </c>
       <c r="O53" t="n">
-        <v>2.704210758209229</v>
+        <v>2.546111345291138</v>
       </c>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
@@ -3384,50 +3384,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2024-07-23 19:20</t>
+          <t>2024-07-23 21:10:00</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="I54" t="n">
-        <v>25.95</v>
+        <v>31.72</v>
       </c>
       <c r="J54" t="n">
-        <v>2.35</v>
+        <v>2.96</v>
       </c>
       <c r="K54" t="n">
-        <v>40.94</v>
+        <v>101.97</v>
       </c>
       <c r="L54" t="n">
-        <v>0.318</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.451</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.625080943107605</v>
+        <v>1.356927633285522</v>
       </c>
       <c r="O54" t="n">
-        <v>2.77298378944397</v>
+        <v>2.557090759277344</v>
       </c>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
@@ -3441,7 +3441,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2024-07-23 19:30</t>
+          <t>2024-07-23 21:20:00</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -3463,16 +3463,16 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="I55" t="n">
-        <v>50.27</v>
+        <v>29.92</v>
       </c>
       <c r="J55" t="n">
-        <v>2.35</v>
+        <v>2.95</v>
       </c>
       <c r="K55" t="n">
-        <v>40.94</v>
+        <v>100.79</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1.53760814666748</v>
+        <v>1.321532964706421</v>
       </c>
       <c r="O55" t="n">
-        <v>2.885339021682739</v>
+        <v>2.556981563568115</v>
       </c>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
@@ -3498,7 +3498,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2024-07-23 19:40</t>
+          <t>2024-07-23 21:30:00</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="I56" t="n">
-        <v>81.92</v>
+        <v>28.75</v>
       </c>
       <c r="J56" t="n">
-        <v>2.35</v>
+        <v>2.91</v>
       </c>
       <c r="K56" t="n">
-        <v>40.94</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -3538,10 +3538,10 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1.605435252189636</v>
+        <v>1.361050724983215</v>
       </c>
       <c r="O56" t="n">
-        <v>2.937855958938599</v>
+        <v>2.53759241104126</v>
       </c>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
@@ -3555,7 +3555,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2024-07-23 19:50</t>
+          <t>2024-07-23 21:40:00</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -3577,16 +3577,16 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>93.47</v>
+        <v>27.61</v>
       </c>
       <c r="J57" t="n">
-        <v>2.34</v>
+        <v>2.87</v>
       </c>
       <c r="K57" t="n">
-        <v>40.13</v>
+        <v>91.59</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3595,10 +3595,10 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1.659320592880249</v>
+        <v>1.357614874839783</v>
       </c>
       <c r="O57" t="n">
-        <v>3.051085710525513</v>
+        <v>2.573524951934814</v>
       </c>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
@@ -3612,7 +3612,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2024-07-23 20:00</t>
+          <t>2024-07-23 21:50:00</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -3634,16 +3634,16 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>2.07</v>
+        <v>1.32</v>
       </c>
       <c r="I58" t="n">
-        <v>89.90000000000001</v>
+        <v>26.5</v>
       </c>
       <c r="J58" t="n">
-        <v>2.34</v>
+        <v>2.83</v>
       </c>
       <c r="K58" t="n">
-        <v>40.13</v>
+        <v>87.13</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -3652,10 +3652,10 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.647294282913208</v>
+        <v>1.432636857032776</v>
       </c>
       <c r="O58" t="n">
-        <v>3.094000339508057</v>
+        <v>2.557263135910034</v>
       </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
@@ -3669,7 +3669,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2024-07-23 20:10</t>
+          <t>2024-07-23 22:00:00</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3691,16 +3691,16 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1.94</v>
+        <v>1.3</v>
       </c>
       <c r="I59" t="n">
-        <v>75.45</v>
+        <v>25.37</v>
       </c>
       <c r="J59" t="n">
-        <v>2.34</v>
+        <v>2.79</v>
       </c>
       <c r="K59" t="n">
-        <v>40.13</v>
+        <v>82.75</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -3709,10 +3709,10 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>1.679632782936096</v>
+        <v>1.378921866416931</v>
       </c>
       <c r="O59" t="n">
-        <v>3.187734365463257</v>
+        <v>2.552320718765259</v>
       </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
@@ -3726,7 +3726,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2024-07-23 20:20</t>
+          <t>2024-07-23 22:10:00</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -3748,16 +3748,16 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="I60" t="n">
-        <v>61.6</v>
+        <v>24.23</v>
       </c>
       <c r="J60" t="n">
-        <v>2.34</v>
+        <v>2.77</v>
       </c>
       <c r="K60" t="n">
-        <v>40.13</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -3766,10 +3766,10 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>1.644819021224976</v>
+        <v>1.296398043632507</v>
       </c>
       <c r="O60" t="n">
-        <v>3.222316741943359</v>
+        <v>2.53627347946167</v>
       </c>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
@@ -3783,7 +3783,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2024-07-23 20:30</t>
+          <t>2024-07-23 22:20:00</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3805,16 +3805,16 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="I61" t="n">
-        <v>51.92</v>
+        <v>23.67</v>
       </c>
       <c r="J61" t="n">
-        <v>2.33</v>
+        <v>2.76</v>
       </c>
       <c r="K61" t="n">
-        <v>39.33</v>
+        <v>79.53</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -3823,10 +3823,10 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>1.667603135108948</v>
+        <v>1.308075308799744</v>
       </c>
       <c r="O61" t="n">
-        <v>3.246699094772339</v>
+        <v>2.525702238082886</v>
       </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
@@ -3840,7 +3840,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2024-07-23 20:40</t>
+          <t>2024-07-23 22:30:00</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3862,16 +3862,16 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="I62" t="n">
-        <v>44.75</v>
+        <v>23.11</v>
       </c>
       <c r="J62" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="K62" t="n">
-        <v>40.13</v>
+        <v>78.47</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3880,10 +3880,10 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.627484440803528</v>
+        <v>1.247061133384705</v>
       </c>
       <c r="O62" t="n">
-        <v>3.298796653747559</v>
+        <v>2.512203216552734</v>
       </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
@@ -3897,7 +3897,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2024-07-23 20:50</t>
+          <t>2024-07-23 22:40:00</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3919,16 +3919,16 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="I63" t="n">
-        <v>38.93</v>
+        <v>22.01</v>
       </c>
       <c r="J63" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="K63" t="n">
-        <v>88.23</v>
+        <v>77.41</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3937,10 +3937,10 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1.509808897972107</v>
+        <v>1.182692050933838</v>
       </c>
       <c r="O63" t="n">
-        <v>3.273085117340088</v>
+        <v>2.502001285552979</v>
       </c>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
@@ -3954,7 +3954,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2024-07-23 21:00</t>
+          <t>2024-07-23 22:50:00</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -3976,16 +3976,16 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="I64" t="n">
-        <v>34.88</v>
+        <v>21.47</v>
       </c>
       <c r="J64" t="n">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="K64" t="n">
-        <v>98.45999999999999</v>
+        <v>76.36</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3994,10 +3994,10 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.497649788856506</v>
+        <v>1.226963877677917</v>
       </c>
       <c r="O64" t="n">
-        <v>3.365260124206543</v>
+        <v>2.502537250518799</v>
       </c>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
@@ -4011,7 +4011,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2024-07-23 21:10</t>
+          <t>2024-07-23 23:00:00</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -4033,16 +4033,16 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="I65" t="n">
-        <v>31.72</v>
+        <v>20.94</v>
       </c>
       <c r="J65" t="n">
-        <v>2.96</v>
+        <v>2.71</v>
       </c>
       <c r="K65" t="n">
-        <v>101.97</v>
+        <v>74.28</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -4051,10 +4051,10 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.503317594528198</v>
+        <v>1.196367979049683</v>
       </c>
       <c r="O65" t="n">
-        <v>3.361884117126465</v>
+        <v>2.493808507919312</v>
       </c>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
@@ -4068,7 +4068,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2024-07-23 21:20</t>
+          <t>2024-07-23 23:10:00</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -4090,16 +4090,16 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="I66" t="n">
-        <v>29.92</v>
+        <v>20.41</v>
       </c>
       <c r="J66" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="K66" t="n">
-        <v>100.79</v>
+        <v>73.25</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -4108,10 +4108,10 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.445578575134277</v>
+        <v>1.17212176322937</v>
       </c>
       <c r="O66" t="n">
-        <v>3.338188171386719</v>
+        <v>2.484206914901733</v>
       </c>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
@@ -4125,7 +4125,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2024-07-23 21:30</t>
+          <t>2024-07-23 23:20:00</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -4147,16 +4147,16 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="I67" t="n">
-        <v>28.75</v>
+        <v>20.41</v>
       </c>
       <c r="J67" t="n">
-        <v>2.91</v>
+        <v>2.69</v>
       </c>
       <c r="K67" t="n">
-        <v>96.15000000000001</v>
+        <v>72.22</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -4165,10 +4165,10 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.338707447052002</v>
+        <v>1.233901381492615</v>
       </c>
       <c r="O67" t="n">
-        <v>3.296223402023315</v>
+        <v>2.486347675323486</v>
       </c>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
@@ -4182,7 +4182,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2024-07-23 21:40</t>
+          <t>2024-07-23 23:30:00</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -4204,16 +4204,16 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="I68" t="n">
-        <v>27.61</v>
+        <v>19.88</v>
       </c>
       <c r="J68" t="n">
-        <v>2.87</v>
+        <v>2.68</v>
       </c>
       <c r="K68" t="n">
-        <v>91.59</v>
+        <v>71.2</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -4222,10 +4222,10 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.312803506851196</v>
+        <v>1.241949439048767</v>
       </c>
       <c r="O68" t="n">
-        <v>3.241755485534668</v>
+        <v>2.457021951675415</v>
       </c>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2024-07-23 21:50</t>
+          <t>2024-07-23 23:40:00</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -4261,16 +4261,16 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="I69" t="n">
-        <v>26.5</v>
+        <v>19.88</v>
       </c>
       <c r="J69" t="n">
-        <v>2.83</v>
+        <v>2.66</v>
       </c>
       <c r="K69" t="n">
-        <v>87.13</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1.367445826530457</v>
+        <v>1.223694682121277</v>
       </c>
       <c r="O69" t="n">
-        <v>3.173375129699707</v>
+        <v>2.439630508422852</v>
       </c>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
@@ -4296,7 +4296,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2024-07-23 22:00</t>
+          <t>2024-07-23 23:50:00</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -4318,16 +4318,16 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="I70" t="n">
-        <v>25.37</v>
+        <v>19.37</v>
       </c>
       <c r="J70" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="K70" t="n">
-        <v>82.75</v>
+        <v>68.17</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -4336,10 +4336,10 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1.34131395816803</v>
+        <v>1.240607142448425</v>
       </c>
       <c r="O70" t="n">
-        <v>3.094263315200806</v>
+        <v>2.489829540252686</v>
       </c>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
@@ -4353,7 +4353,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2024-07-23 22:10</t>
+          <t>2024-07-24 00:00:00</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -4375,16 +4375,16 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="I71" t="n">
-        <v>24.23</v>
+        <v>18.85</v>
       </c>
       <c r="J71" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="K71" t="n">
-        <v>80.59999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.340293169021606</v>
+        <v>1.219378590583801</v>
       </c>
       <c r="O71" t="n">
-        <v>3.010372877120972</v>
+        <v>2.460252046585083</v>
       </c>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
@@ -4410,7 +4410,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2024-07-23 22:20</t>
+          <t>2024-07-24 00:10:00</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -4432,16 +4432,16 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="I72" t="n">
-        <v>23.67</v>
+        <v>18.85</v>
       </c>
       <c r="J72" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="K72" t="n">
-        <v>79.53</v>
+        <v>65.2</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -4450,10 +4450,10 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1.327605009078979</v>
+        <v>1.224920749664307</v>
       </c>
       <c r="O72" t="n">
-        <v>2.941696166992188</v>
+        <v>2.451065063476562</v>
       </c>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
@@ -4467,7 +4467,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2024-07-23 22:30</t>
+          <t>2024-07-24 00:20:00</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -4489,16 +4489,16 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="I73" t="n">
-        <v>23.11</v>
+        <v>18.35</v>
       </c>
       <c r="J73" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="K73" t="n">
-        <v>78.47</v>
+        <v>64.22</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -4507,10 +4507,10 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1.306854248046875</v>
+        <v>1.208103179931641</v>
       </c>
       <c r="O73" t="n">
-        <v>2.880031824111938</v>
+        <v>2.4484703540802</v>
       </c>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
